--- a/etf_holdings/2026-10-20_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.47%333,000</t>
+          <t>8.48%333,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.47%</t>
+          <t>8.48%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5125</v>
+        <v>1055</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.13%113,000</t>
+          <t>6.21%526,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.21%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>113000</v>
+        <v>526000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3320</v>
+        <v>3325</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.13%176,000</t>
+          <t>6.16%176,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.75%1120</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1120</v>
+        <v>4945</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.03%526,000</t>
+          <t>6.11%113,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>6.11%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>526000</v>
+        <v>113000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.8%982</t>
+          <t>-3.77%945</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>982</v>
+        <v>945</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.88%464,000</t>
+          <t>4.81%464,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.81%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.03%15980</t>
+          <t>-0.5%15900</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>15980</v>
+        <v>15900</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.43%25,600</t>
+          <t>4.32%25,600</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.93%1630</t>
+          <t>-4.91%1550</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1630</v>
+        <v>1550</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.23%249,000</t>
+          <t>4.28%249,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.28%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.58%5235</t>
+          <t>-6.4%4900</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5235</v>
+        <v>4900</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.16%76,000</t>
+          <t>4.20%76,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.20%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.85%1380</t>
+          <t>-5.43%1305</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1380</v>
+        <v>1305</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.00%281,000</t>
+          <t>4.09%281,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.09%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+4.68%7830</t>
+          <t>-1.09%7745</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+4.68%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7830</v>
+        <v>7745</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.54%45,000</t>
+          <t>3.72%45,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.14%303.5</t>
+          <t>-2.47%296</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>303.5</v>
+        <v>296</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.73%846,000</t>
+          <t>2.71%846,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.57%436</t>
+          <t>-3.21%422</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.71%577,000</t>
+          <t>2.65%577,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.8%547</t>
+          <t>0%547</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.50%427,000</t>
+          <t>2.46%427,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1885</v>
+        <v>1925</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.92%99,191</t>
+          <t>1.97%99,191</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:23</t>
+          <t>2026-10-20 21:44:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.13%131.5</t>
+          <t>-3.42%127</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>131.5</v>
+        <v>127</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.86%1,333,000</t>
+          <t>1.85%1,333,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.35%1405</t>
+          <t>-6.05%1320</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-6.05%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1405</v>
+        <v>1320</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6245</v>
+        <v>5975</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.68%25,000</t>
+          <t>1.65%25,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.87%1525</t>
+          <t>-1.04%858</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1525</v>
+        <v>858</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.65%100,000</t>
+          <t>1.63%178,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>100000</v>
+        <v>178000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.8%867</t>
+          <t>+1.31%1545</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>867</v>
+        <v>1545</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.64%178,000</t>
+          <t>1.61%100,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>178000</v>
+        <v>100000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.72%155.5</t>
+          <t>+0.74%684</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>155.5</v>
+        <v>684</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.52%896,000</t>
+          <t>1.48%206,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>896000</v>
+        <v>206000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.88%679</t>
+          <t>-1.93%152.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>679</v>
+        <v>152.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.48%206,000</t>
+          <t>1.47%896,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>206000</v>
+        <v>896000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4205</v>
+        <v>4150</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.47%33,000</t>
+          <t>1.46%33,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.31%116</t>
+          <t>-8.19%106.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-8.19%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>116</v>
+        <v>106.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.41%1,092,000</t>
+          <t>1.34%1,092,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3406玉晶光</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.69%1045</t>
+          <t>-3.11%2490</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1045</v>
+        <v>2490</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.32%116,000</t>
+          <t>1.33%49,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>116000</v>
+        <v>49000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3406玉晶光</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.98%2570</t>
+          <t>-0.48%1040</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2570</v>
+        <v>1040</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.31%49,000</t>
+          <t>1.28%116,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>49000</v>
+        <v>116000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+3.78%2335</t>
+          <t>-1.93%2290</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2335</v>
+        <v>2290</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.21%51,000</t>
+          <t>1.26%51,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.26%2005</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2005</v>
+        <v>1970</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.17%56,000</t>
+          <t>1.18%56,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.79%482</t>
+          <t>-1.45%475</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.13%214,000</t>
+          <t>1.09%214,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:25</t>
+          <t>2026-10-20 21:45:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.35%9920</t>
+          <t>+1.81%10100</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9920</v>
+        <v>10100</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.98%247</t>
+          <t>-3.64%238</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.98%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.05%396,000</t>
+          <t>1.03%396,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.81%1385</t>
+          <t>-5.96%489</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1385</v>
+        <v>489</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.98%64,000</t>
+          <t>1.00%183,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>64000</v>
+        <v>183000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+5.26%520</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+5.26%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>520</v>
+        <v>1330</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.95%183,000</t>
+          <t>0.93%64,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>183000</v>
+        <v>64000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.2%577</t>
+          <t>-1.73%567</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.3%491.5</t>
+          <t>-1.22%485.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>491.5</v>
+        <v>485.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.53%6560</t>
+          <t>+1.37%6650</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6560</v>
+        <v>6650</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.78%11,000</t>
+          <t>0.76%11,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.19%264</t>
+          <t>-0.76%262</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.93%182.5</t>
+          <t>-1.64%179.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>182.5</v>
+        <v>179.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.61%310,000</t>
+          <t>0.60%310,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.19%258</t>
+          <t>-4.26%247</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-4.26%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.25%2005</t>
+          <t>-0.25%2000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-3.35%491</t>
+          <t>-1.63%483</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.52%98,000</t>
+          <t>0.51%98,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0%248</t>
+          <t>-1.81%243.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>248</v>
+        <v>243.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.9%1100</t>
+          <t>-0.91%1090</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.2%51</t>
+          <t>-2.06%49.95</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>51</v>
+        <v>49.95</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.44%829,000</t>
+          <t>0.45%829,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:26</t>
+          <t>2026-10-20 21:45:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.93%73</t>
+          <t>-0.41%72.7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>73</v>
+        <v>72.7</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.42%526,000</t>
+          <t>0.41%526,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:27</t>
+          <t>2026-10-20 21:45:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.4%1250</t>
+          <t>-5.2%1185</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1250</v>
+        <v>1185</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:27</t>
+          <t>2026-10-20 21:45:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.39%163.5</t>
+          <t>-2.14%160</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>163.5</v>
+        <v>160</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:27</t>
+          <t>2026-10-20 21:45:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.99%1975</t>
+          <t>-2.53%1925</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1975</v>
+        <v>1925</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.30%14,000</t>
+          <t>0.29%14,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:27</t>
+          <t>2026-10-20 21:45:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.53%225.5</t>
+          <t>-2.88%219</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>225.5</v>
+        <v>219</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:27</t>
+          <t>2026-10-20 21:45:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.63%157.5</t>
+          <t>-2.54%153.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>157.5</v>
+        <v>153.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-20_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:44:59</t>
+          <t>2026-10-20 21:54:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:00</t>
+          <t>2026-10-20 21:55:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:02</t>
+          <t>2026-10-20 21:55:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:03</t>
+          <t>2026-10-20 21:55:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:03</t>
+          <t>2026-10-20 21:55:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:03</t>
+          <t>2026-10-20 21:55:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:03</t>
+          <t>2026-10-20 21:55:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:45:03</t>
+          <t>2026-10-20 21:55:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-20_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:59</t>
+          <t>2026-10-20 22:20:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:00</t>
+          <t>2026-10-20 22:20:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:01</t>
+          <t>2026-10-20 22:20:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:03</t>
+          <t>2026-10-20 22:20:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:03</t>
+          <t>2026-10-20 22:20:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:03</t>
+          <t>2026-10-20 22:20:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:03</t>
+          <t>2026-10-20 22:20:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:55:03</t>
+          <t>2026-10-20 22:20:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
